--- a/p6_deployment/data/germany/predicciones.xlsx
+++ b/p6_deployment/data/germany/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX10"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,160 +520,40 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>dif_prob_mod_bm</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>result_to_bet</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>dif_prob_result_to_bet</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>prob_result_to_bet</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_home</t>
+          <t>odd_to_bet</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>strategy</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>multiplier</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_start_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_start_away</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>result_to_bet</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_prob_result_to_bet</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>prob_result_to_bet</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>odd_to_bet</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>strategy</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>multiplier</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -729,114 +609,42 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.489085559197683</v>
+        <v>0.7550082860716901</v>
       </c>
       <c r="P2" t="n">
-        <v>0.457447753801992</v>
+        <v>0.2068343636710439</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05346668700032515</v>
+        <v>0.03815735025726579</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>25.61666666666667</v>
+        <v>0.003241634440356522</v>
       </c>
       <c r="T2" t="n">
-        <v>185.1861111111111</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>0.003241634440356522</v>
       </c>
       <c r="V2" t="n">
-        <v>80.90833333333333</v>
+        <v>0.7550082860716901</v>
       </c>
       <c r="W2" t="n">
-        <v>29851388.88888889</v>
-      </c>
-      <c r="X2" t="n">
-        <v>83.90833333333333</v>
+        <v>1.27</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
       </c>
       <c r="Y2" t="n">
-        <v>25.63703703703703</v>
+        <v>60.40066288573521</v>
       </c>
       <c r="Z2" t="n">
-        <v>186.037037037037</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.451851851851852</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>74.57777777777778</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>6745185.185185186</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>77.25185185185185</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>22.27232142857143</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>181.5178571428571</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.696428571428572</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>77.70535714285714</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>35131250</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>84.36607142857142</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>23.83333333333333</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>184.1666666666667</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.208333333333333</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>70.58333333333333</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>3646875</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>76.29166666666667</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-0.2626810924336506</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-0.2626810924336506</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.489085559197683</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AW2" t="n">
-        <v>39.12684473581464</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>39.12684473581464</v>
+        <v>60.40066288573521</v>
       </c>
     </row>
     <row r="3">
@@ -889,114 +697,42 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6096313199782291</v>
+        <v>0.7176184566796064</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2868189353408666</v>
+        <v>0.2025585106781702</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1035497446809043</v>
+        <v>0.07982303264222329</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>25.03030303030303</v>
+        <v>-0.1138671309035421</v>
       </c>
       <c r="T3" t="n">
-        <v>184.9393939393939</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>2.212121212121212</v>
+        <v>-0.1138671309035421</v>
       </c>
       <c r="V3" t="n">
-        <v>79.33333333333333</v>
+        <v>0.7176184566796064</v>
       </c>
       <c r="W3" t="n">
-        <v>28430303.03030303</v>
-      </c>
-      <c r="X3" t="n">
-        <v>83.06060606060606</v>
+        <v>1.14</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
       </c>
       <c r="Y3" t="n">
-        <v>25.56969696969697</v>
+        <v>57.40947653436852</v>
       </c>
       <c r="Z3" t="n">
-        <v>187.1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>70.58787878787881</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2434318.181818182</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>74.16666666666667</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>25.14814814814815</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>183.9259259259259</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>76.74074074074075</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>18696296.2962963</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>81.55555555555556</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>25.59722222222222</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>186.3564814814815</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>68.08333333333333</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1538310.185185185</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>71.2175925925926</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-0.2218542676049194</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>-0.2218542676049194</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0.6096313199782291</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AW3" t="n">
-        <v>48.77050559825832</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>48.77050559825832</v>
+        <v>57.40947653436852</v>
       </c>
     </row>
     <row r="4">
@@ -1046,117 +782,45 @@
         <v>0.0512820512820511</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3561928627487634</v>
+        <v>0.4228908692381797</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3643683802155721</v>
+        <v>0.3480615453901542</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2794387570356646</v>
+        <v>0.229047585371666</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>24.55555555555556</v>
+        <v>0.05703721070159429</v>
       </c>
       <c r="T4" t="n">
-        <v>183.2222222222223</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.703703703703704</v>
+        <v>0.05703721070159429</v>
       </c>
       <c r="V4" t="n">
-        <v>77.55555555555556</v>
+        <v>0.4228908692381797</v>
       </c>
       <c r="W4" t="n">
-        <v>16551851.85185185</v>
-      </c>
-      <c r="X4" t="n">
-        <v>81.18518518518518</v>
+        <v>2.6</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
       </c>
       <c r="Y4" t="n">
-        <v>24.6</v>
+        <v>33.83126953905438</v>
       </c>
       <c r="Z4" t="n">
-        <v>182.5333333333333</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>29816666.66666667</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>84.03333333333335</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>24.875</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>183.75</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.416666666666667</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>71.33333333333333</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>4554166.666666667</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>77.41666666666667</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>25.77777777777778</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>185.925925925926</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.703703703703704</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>76.51851851851852</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>15377777.77777778</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>80.5925925925926</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0.1107098436302061</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0.1107098436302061</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0.3643683802155721</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AW4" t="n">
-        <v>29.14947041724577</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>29.14947041724577</v>
+        <v>33.83126953905438</v>
       </c>
     </row>
     <row r="5">
@@ -1209,114 +873,42 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4188793039244039</v>
+        <v>0.4955677047040607</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3330967265076525</v>
+        <v>0.3081133778056834</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2480239695679435</v>
+        <v>0.1963189174902557</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>25.66666666666666</v>
+        <v>0.08351123770673141</v>
       </c>
       <c r="T5" t="n">
-        <v>186.6363636363636</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0.08351123770673141</v>
       </c>
       <c r="V5" t="n">
-        <v>72.90909090909091</v>
+        <v>0.4955677047040607</v>
       </c>
       <c r="W5" t="n">
-        <v>4484090.909090909</v>
-      </c>
-      <c r="X5" t="n">
-        <v>75.33333333333333</v>
+        <v>2.3</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
       </c>
       <c r="Y5" t="n">
-        <v>24</v>
+        <v>39.64541637632485</v>
       </c>
       <c r="Z5" t="n">
-        <v>185.1212121212121</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.363636363636364</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>72.48484848484848</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>6006060.606060606</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>78.27272727272727</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>27.51851851851852</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>182.6296296296296</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>67.62962962962962</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1204629.62962963</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>69.55555555555556</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>26.2962962962963</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>184.4444444444444</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.296296296296296</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>69.25925925925925</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>2702592.592592593</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>74.7037037037037</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0.006822836927074583</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0.006822836927074583</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0.4188793039244039</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AW5" t="n">
-        <v>33.51034431395231</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>33.51034431395231</v>
+        <v>39.64541637632485</v>
       </c>
     </row>
     <row r="6">
@@ -1369,114 +961,42 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1263894353574463</v>
+        <v>0.2293291797237196</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5516242080015674</v>
+        <v>0.4027794943306746</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3219863566409864</v>
+        <v>0.367891325945606</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>26.63636363636364</v>
+        <v>0.1832659933580335</v>
       </c>
       <c r="T6" t="n">
-        <v>185.1212121212121</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.787878787878788</v>
+        <v>0.1832659933580335</v>
       </c>
       <c r="V6" t="n">
-        <v>75.09090909090908</v>
+        <v>0.4027794943306746</v>
       </c>
       <c r="W6" t="n">
-        <v>8639393.939393939</v>
-      </c>
-      <c r="X6" t="n">
-        <v>78.75757575757576</v>
+        <v>4.33</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
       </c>
       <c r="Y6" t="n">
-        <v>27.93939393939394</v>
+        <v>32.22235954645397</v>
       </c>
       <c r="Z6" t="n">
-        <v>185.4242424242424</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.060606060606061</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>81.93939393939394</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>36981818.18181818</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>84.24242424242424</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>24.03703703703704</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>186.2592592592593</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>70.5925925925926</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>4445370.37037037</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>77.29629629629629</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>24.59788359788359</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>182.0291005291006</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>2.125661375661375</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>77.22156084656085</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>24202562.83068783</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>82.55291005291006</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0.3321107070289263</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0.3321107070289263</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0.5516242080015674</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AW6" t="n">
-        <v>44.12993664012539</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>44.12993664012539</v>
+        <v>32.22235954645397</v>
       </c>
     </row>
     <row r="7">
@@ -1526,117 +1046,45 @@
         <v>0.06252927400468389</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.424966797714862</v>
+        <v>0.5855998191128851</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4642043065973396</v>
+        <v>0.334431373600839</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1108288956877984</v>
+        <v>0.07996880728627595</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>24.3030303030303</v>
+        <v>-0.1858350497431872</v>
       </c>
       <c r="T7" t="n">
-        <v>184.7878787878788</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.484848484848485</v>
+        <v>-0.1858350497431872</v>
       </c>
       <c r="V7" t="n">
-        <v>76</v>
+        <v>0.5855998191128851</v>
       </c>
       <c r="W7" t="n">
-        <v>11778787.87878788</v>
-      </c>
-      <c r="X7" t="n">
-        <v>79.36363636363636</v>
+        <v>1.22</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
       </c>
       <c r="Y7" t="n">
-        <v>24.85151515151515</v>
+        <v>46.84798552903081</v>
       </c>
       <c r="Z7" t="n">
-        <v>184.6727272727273</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.421212121212121</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>74.54545454545455</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>7250303.03030303</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>77.9969696969697</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>24.92857142857143</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>182.8809523809524</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.303571428571429</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>70.08333333333333</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>4427380.952380952</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>74.32142857142857</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>22.47619047619048</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>184.0952380952381</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.327380952380953</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>71.98214285714285</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>6937797.619047619</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>79.00595238095238</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0.3297542294538528</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0.3297542294538528</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0.4642043065973396</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AW7" t="n">
-        <v>37.13634452778717</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>37.13634452778717</v>
+        <v>46.84798552903081</v>
       </c>
     </row>
     <row r="8">
@@ -1689,114 +1137,42 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4274449614061621</v>
+        <v>0.4716002768413151</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3375187194627641</v>
+        <v>0.3005622218462861</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.235036319131074</v>
+        <v>0.2278375013123988</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>26.90909090909091</v>
+        <v>0.04302884826988651</v>
       </c>
       <c r="T8" t="n">
-        <v>184.3030303030303</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.636363636363636</v>
+        <v>0.04302884826988651</v>
       </c>
       <c r="V8" t="n">
-        <v>76.09090909090908</v>
+        <v>0.4716002768413151</v>
       </c>
       <c r="W8" t="n">
-        <v>9112121.212121213</v>
-      </c>
-      <c r="X8" t="n">
-        <v>78.30303030303031</v>
+        <v>2.2</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
       </c>
       <c r="Y8" t="n">
-        <v>27.36363636363636</v>
+        <v>37.72802214730521</v>
       </c>
       <c r="Z8" t="n">
-        <v>183.5151515151515</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.696969696969697</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>75.57575757575758</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>9124242.424242424</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>77.27272727272727</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>27.54166666666667</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>184.9953703703704</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.574074074074074</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>73.74537037037037</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>4630787.037037037</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>75.87037037037037</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>24.15079365079366</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>185.2222222222223</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.34920634920635</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>72.2936507936508</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>3826984.126984127</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>76.19047619047619</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>-0.001126467165266543</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>-0.001126467165266543</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0.4274449614061621</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AW8" t="n">
-        <v>34.19559691249297</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>34.19559691249297</v>
+        <v>37.72802214730521</v>
       </c>
     </row>
     <row r="9">
@@ -1846,117 +1222,45 @@
         <v>0.05738797268032658</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2568092575969464</v>
+        <v>0.3415754307328592</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3060396735930759</v>
+        <v>0.3829313436432906</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4371510688099774</v>
+        <v>0.2754932256238501</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>26.18181818181818</v>
+        <v>0.1202294925208015</v>
       </c>
       <c r="T9" t="n">
-        <v>183.1363636363636</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.181818181818182</v>
+        <v>0.1202294925208015</v>
       </c>
       <c r="V9" t="n">
-        <v>73.11363636363636</v>
+        <v>0.3829313436432906</v>
       </c>
       <c r="W9" t="n">
-        <v>4792613.636363637</v>
-      </c>
-      <c r="X9" t="n">
-        <v>75.90909090909091</v>
+        <v>3.6</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
       </c>
       <c r="Y9" t="n">
-        <v>27.88888888888889</v>
+        <v>30.63450749146325</v>
       </c>
       <c r="Z9" t="n">
-        <v>182.4074074074074</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.259259259259259</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>73.25925925925925</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3616666.666666667</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>75.03703703703702</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>24.19047619047619</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>185.5912698412698</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.063492063492063</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>66.05952380952381</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1753174.603174603</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>72.52777777777777</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>27.10185185185185</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>183.8611111111111</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.041666666666667</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>69.84722222222223</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>2045370.37037037</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>73.07870370370371</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0.1110384260372323</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0.1110384260372323</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0.4371510688099774</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AW9" t="n">
-        <v>34.97208550479819</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>34.97208550479819</v>
+        <v>30.63450749146325</v>
       </c>
     </row>
     <row r="10">
@@ -2009,114 +1313,42 @@
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.56757835520559</v>
+        <v>0.587533458537466</v>
       </c>
       <c r="P10" t="n">
-        <v>0.312790561808484</v>
+        <v>0.3047913814091326</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1196310829859259</v>
+        <v>0.1076751600534013</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>25.1</v>
+        <v>0.3060672157845203</v>
       </c>
       <c r="T10" t="n">
-        <v>186.7333333333333</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6</v>
+        <v>0.3060672157845203</v>
       </c>
       <c r="V10" t="n">
-        <v>76.16666666666666</v>
+        <v>0.587533458537466</v>
       </c>
       <c r="W10" t="n">
-        <v>11725000</v>
-      </c>
-      <c r="X10" t="n">
-        <v>80.03333333333333</v>
+        <v>3.4</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
       </c>
       <c r="Y10" t="n">
-        <v>25.75757575757575</v>
+        <v>47.00267668299728</v>
       </c>
       <c r="Z10" t="n">
-        <v>183.5757575757576</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.575757575757575</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>74.42424242424242</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>6700000</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>78.36363636363637</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>25.03703703703703</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>183.5555555555555</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.296296296296296</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>73.77777777777779</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>7732407.407407408</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>78.14814814814815</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>26.29629629629629</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>185.7407407407407</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.481481481481482</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>71.62962962962962</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>3866666.666666667</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>75.92592592592594</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0.2861121124526443</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0.2861121124526443</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0.56757835520559</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AW10" t="n">
-        <v>45.4062684164472</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>45.4062684164472</v>
+        <v>47.00267668299728</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/germany/predicciones.xlsx
+++ b/p6_deployment/data/germany/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:AB28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,100 +460,110 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>odds_home</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>odds_draw</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>odds_away</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>prob_home_bm</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>prob_draw_bm</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>prob_away_bm</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>overround</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>predicted_result</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>prob_class_1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>prob_class_0</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>prob_class_2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>copiado_formaciones</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>result_to_bet</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_prob_result_to_bet</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>prob_result_to_bet</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>odd_to_bet</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>multiplier</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -562,793 +572,1805 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>r7QOmnxn</t>
+          <t>pWQQJq6l</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45430.4375</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bayer leverkusen</t>
+          <t>hallescher</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>augsburg</t>
+          <t>st  pauli</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>59</v>
       </c>
       <c r="F2" t="n">
-        <v>591</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="H2" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="I2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.7517666516313336</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.152758983611487</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.09547436475717938</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.04740157480314955</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.7550082860716901</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.2068343636710439</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.03815735025726579</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.003241634440356522</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
-        <v>0.003241634440356522</v>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7550082860716901</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>60.40066288573521</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>60.40066288573521</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fBoFTriU</t>
+          <t>hIsO3XFj</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45430.4375</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dortmund</t>
+          <t>wehen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>darmstadt</t>
+          <t>mainz</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>591</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="H3" t="n">
-        <v>9</v>
-      </c>
-      <c r="I3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.8314855875831485</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.1053215077605321</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.06319290465631928</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.05497076023391823</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.7176184566796064</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>0.2025585106781702</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.07982303264222329</v>
+        <v>0.5188744203040679</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0.1182421255999352</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1138671309035421</v>
+        <v>0.3628834540959966</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
-        <v>-0.1138671309035421</v>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7176184566796064</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y3" t="n">
-        <v>57.40947653436852</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>57.40947653436852</v>
+        <v>-1</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>0.4811255796959321</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>33.67879057871524</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>33.67879057871524</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>QVFTn6ih</t>
+          <t>EF8gXauC</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45430.4375</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>wurzburger kickers</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>hoffenheim</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>59</v>
       </c>
       <c r="F4" t="n">
-        <v>591</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.3658536585365854</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.2536585365853659</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.3804878048780488</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.0512820512820511</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.4228908692381797</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.3480615453901542</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.229047585371666</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.05703721070159429</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
-        <v>0.05703721070159429</v>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4228908692381797</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y4" t="n">
-        <v>33.83126953905438</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>33.83126953905438</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8EBlrr6N</t>
+          <t>lONsG15D</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45430.4375</v>
+        <v>45520.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>heidenheim</t>
+          <t>ulm</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>fc koln</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>59</v>
       </c>
       <c r="F5" t="n">
-        <v>591</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.4120564669973293</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.2369324685234643</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.3510110644792064</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.05515297906602257</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.4955677047040607</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.3081133778056834</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.1963189174902557</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.08351123770673141</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>0.08351123770673141</v>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4955677047040607</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y5" t="n">
-        <v>39.64541637632485</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>39.64541637632485</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YeJyopM4</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45430.4375</v>
+        <v>45521.33333333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hoffenheim</t>
+          <t>aue</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>bayern munich</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>59</v>
       </c>
       <c r="F6" t="n">
-        <v>591</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.316831153070512</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.2195135009726411</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.4636553459568469</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.05208509359920388</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.2293291797237196</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.4027794943306746</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.367891325945606</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.1832659933580335</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.1832659933580335</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4027794943306746</v>
-      </c>
-      <c r="W6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y6" t="n">
-        <v>32.22235954645397</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>32.22235954645397</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fB7pqOjH</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45430.4375</v>
+        <v>45521.33333333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>stuttgart</t>
+          <t>schott mainz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>b  monchengladbach</t>
+          <t>greuther furth</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>591</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="H7" t="n">
-        <v>7</v>
-      </c>
-      <c r="I7" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.7714348688560723</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.1344500771434869</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.09411505400044082</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.06252927400468389</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.5855998191128851</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.334431373600839</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.07996880728627595</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.1858350497431872</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>-0.1858350497431872</v>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5855998191128851</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y7" t="n">
-        <v>46.84798552903081</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>46.84798552903081</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WWMKlSMu</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45430.4375</v>
+        <v>45521.4375</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>union berlin</t>
+          <t>aalen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>freiburg</t>
+          <t>schalke</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>59</v>
       </c>
       <c r="F8" t="n">
-        <v>591</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.4285714285714286</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.2857142857142858</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.2857142857142858</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.06060606060606055</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.4716002768413151</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.3005622218462861</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.2278375013123988</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.04302884826988651</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>0.04302884826988651</v>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4716002768413151</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y8" t="n">
-        <v>37.72802214730521</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>37.72802214730521</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CnIup4yB</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45430.4375</v>
+        <v>45521.4375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>greifswald</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>bochum</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>591</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.4111855061047657</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2627018511224892</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.3261126427727452</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.05738797268032658</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.3415754307328592</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.3829313436432906</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.2754932256238501</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.1202294925208015</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.1202294925208015</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3829313436432906</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y9" t="n">
-        <v>30.63450749146325</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>30.63450749146325</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>4MEXoQ6b</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45430.4375</v>
+        <v>45521.4375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wolfsburg</t>
+          <t>ingolstadt</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>mainz</t>
+          <t>kaiserslautern</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>591</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.2814662427529456</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.2734243501028614</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.4451094071441931</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.04494821184287656</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.587533458537466</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.3047913814091326</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.1076751600534013</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.3060672157845203</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>0.3060672157845203</v>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.587533458537466</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X10" t="inlineStr">
+        <v>-100</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>MZjh9ghT</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>rw essen</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>rb leipzig</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" t="n">
+        <v>593</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>f1nnRRDE</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>vfl osnabruck</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>freiburg</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F12" t="n">
+        <v>593</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.4359746750938062</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.1944536237293595</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.3695717011768343</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>0.5640253249061937</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA12" t="n">
+        <v>39.48177274343356</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>39.48177274343356</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>8QPARz8c</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>villingen</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>heidenheim</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>59</v>
+      </c>
+      <c r="F13" t="n">
+        <v>593</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hzyf0b9b</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45521.54166666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>alemannia aachen</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>holstein kiel</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>59</v>
+      </c>
+      <c r="F14" t="n">
+        <v>593</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>CpiTEcOi</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45521.54166666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>arminia bielefeld</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>hannover</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>59</v>
+      </c>
+      <c r="F15" t="n">
+        <v>593</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8CpxDyg4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45521.54166666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>I1Vk6k3R</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>dortmund</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>59</v>
+      </c>
+      <c r="F16" t="n">
+        <v>593</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6q2yrHgU</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45522.33333333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>saarbrucken</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>nurnberg</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>59</v>
+      </c>
+      <c r="F17" t="n">
+        <v>593</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AiJ3kset</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45522.33333333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>viktoria berlin</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>augsburg</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>59</v>
+      </c>
+      <c r="F18" t="n">
+        <v>593</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>YV3TqwPH</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>bremer</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>paderborn</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>59</v>
+      </c>
+      <c r="F19" t="n">
+        <v>593</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>l0ueP5rR</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>hansa rostock</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>hertha berlin</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>59</v>
+      </c>
+      <c r="F20" t="n">
+        <v>593</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.5390186043250673</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.1750954754266535</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.2858859202482793</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="n">
+        <v>0.4609813956749327</v>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA20" t="n">
+        <v>32.26869769724529</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>32.26869769724529</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>t2AoZLAa</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>E3xs5mIe</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>elversberg</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>59</v>
+      </c>
+      <c r="F21" t="n">
+        <v>593</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>jFMCm08e</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>regensburg</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>bochum</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>59</v>
+      </c>
+      <c r="F22" t="n">
+        <v>593</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>tvOIPExA</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>sandhausen</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>fc koln</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>59</v>
+      </c>
+      <c r="F23" t="n">
+        <v>593</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>KSwfVwAO</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>teutonia ottensen</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>darmstadt</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>59</v>
+      </c>
+      <c r="F24" t="n">
+        <v>593</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>pzHxyrtm</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45522.54166666666</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>lotte</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>karlsruher sc</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>59</v>
+      </c>
+      <c r="F25" t="n">
+        <v>593</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>dCPKovw8</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45522.54166666666</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>meppen</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>hamburger sv</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>59</v>
+      </c>
+      <c r="F26" t="n">
+        <v>593</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>vXAKoaf5</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45522.54166666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>sg dynamo dresden</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>dusseldorf</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>59</v>
+      </c>
+      <c r="F27" t="n">
+        <v>593</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>fcxqFy2l</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>bayer leverkusen</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>59</v>
+      </c>
+      <c r="F28" t="n">
+        <v>594</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>super cup</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.5510584327947249</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.2272798605305432</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.221661706674732</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.01379306554446913</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.4062443710357611</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.1506237439840955</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.4431318849801436</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.2214701783054115</v>
+      </c>
+      <c r="V28" t="n">
+        <v>2</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.2214701783054115</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.4431318849801436</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="Z28" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y10" t="n">
-        <v>47.00267668299728</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>47.00267668299728</v>
+      <c r="AA28" t="n">
+        <v>31.01923194861005</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>31.01923194861005</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/germany/predicciones.xlsx
+++ b/p6_deployment/data/germany/predicciones.xlsx
@@ -627,7 +627,7 @@
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr"/>
@@ -676,39 +676,39 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5188744203040679</v>
+        <v>0.09682504138939453</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1182421255999352</v>
+        <v>0.118414317596338</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3628834540959966</v>
+        <v>0.7847606410142675</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>0.4811255796959321</v>
+        <v>0.2152393589857325</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>33.67879057871524</v>
+        <v>5.761967949286626</v>
       </c>
       <c r="AB3" t="n">
-        <v>33.67879057871524</v>
+        <v>5.761967949286626</v>
       </c>
     </row>
     <row r="4">
@@ -769,7 +769,7 @@
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr"/>
@@ -833,7 +833,7 @@
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr"/>
@@ -897,7 +897,7 @@
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr"/>
@@ -961,7 +961,7 @@
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr"/>
@@ -1025,7 +1025,7 @@
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr"/>
@@ -1089,7 +1089,7 @@
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr"/>
@@ -1153,7 +1153,7 @@
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr"/>
@@ -1217,7 +1217,7 @@
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr"/>
@@ -1266,39 +1266,39 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4359746750938062</v>
+        <v>0.06117359204943087</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1944536237293595</v>
+        <v>0.08600848854088686</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3695717011768343</v>
+        <v>0.8528179194096822</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
-        <v>0.5640253249061937</v>
+        <v>0.1471820805903178</v>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>39.48177274343356</v>
+        <v>2.35910402951589</v>
       </c>
       <c r="AB12" t="n">
-        <v>39.48177274343356</v>
+        <v>2.35910402951589</v>
       </c>
     </row>
     <row r="13">
@@ -1359,7 +1359,7 @@
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr"/>
@@ -1423,7 +1423,7 @@
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr"/>
@@ -1487,7 +1487,7 @@
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr"/>
@@ -1615,7 +1615,7 @@
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr"/>
@@ -1679,7 +1679,7 @@
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr"/>
@@ -1743,7 +1743,7 @@
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr"/>
@@ -1792,39 +1792,39 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.5390186043250673</v>
+        <v>0.1778936471174248</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1750954754266535</v>
+        <v>0.1134025292271878</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2858859202482793</v>
+        <v>0.7087038236553874</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
-        <v>0.4609813956749327</v>
+        <v>0.2912961763446126</v>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA20" t="n">
-        <v>32.26869769724529</v>
+        <v>9.564808817230629</v>
       </c>
       <c r="AB20" t="n">
-        <v>32.26869769724529</v>
+        <v>9.564808817230629</v>
       </c>
     </row>
     <row r="21">
@@ -1885,7 +1885,7 @@
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr"/>
@@ -1949,7 +1949,7 @@
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr"/>
@@ -2013,7 +2013,7 @@
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr"/>
@@ -2077,7 +2077,7 @@
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr"/>
@@ -2141,7 +2141,7 @@
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr"/>
@@ -2205,7 +2205,7 @@
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr"/>
@@ -2269,7 +2269,7 @@
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr"/>
@@ -2332,45 +2332,45 @@
         <v>0.01379306554446913</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.4062443710357611</v>
+        <v>0.7990466275754536</v>
       </c>
       <c r="R28" t="n">
-        <v>0.1506237439840955</v>
+        <v>0.03928553527936484</v>
       </c>
       <c r="S28" t="n">
-        <v>0.4431318849801436</v>
+        <v>0.1616678371451817</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0.2214701783054115</v>
+        <v>0.2479881947807288</v>
       </c>
       <c r="V28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>0.2214701783054115</v>
+        <v>0.2479881947807288</v>
       </c>
       <c r="X28" t="n">
-        <v>0.4431318849801436</v>
+        <v>0.7990466275754536</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.45</v>
+        <v>1.79</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
       <c r="AA28" t="n">
-        <v>31.01923194861005</v>
+        <v>34.95233137877268</v>
       </c>
       <c r="AB28" t="n">
-        <v>31.01923194861005</v>
+        <v>34.95233137877268</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/germany/predicciones.xlsx
+++ b/p6_deployment/data/germany/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB28"/>
+  <dimension ref="A1:AB32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -679,13 +679,13 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.09682504138939453</v>
+        <v>0.09632788562397251</v>
       </c>
       <c r="R3" t="n">
-        <v>0.118414317596338</v>
+        <v>0.1182393982592243</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7847606410142675</v>
+        <v>0.7854327161168032</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -696,7 +696,7 @@
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>0.2152393589857325</v>
+        <v>0.2145672838831968</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>5.761967949286626</v>
+        <v>0.8110177206963003</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.761967949286626</v>
+        <v>0.8110177206963003</v>
       </c>
     </row>
     <row r="4">
@@ -1269,13 +1269,13 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.06117359204943087</v>
+        <v>0.06117359204943089</v>
       </c>
       <c r="R12" t="n">
-        <v>0.08600848854088686</v>
+        <v>0.08600848854088683</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8528179194096822</v>
+        <v>0.8528179194096823</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
-        <v>0.1471820805903178</v>
+        <v>0.1471820805903177</v>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr">
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>2.35910402951589</v>
+        <v>0.5563162909433954</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.35910402951589</v>
+        <v>0.5563162909433954</v>
       </c>
     </row>
     <row r="13">
@@ -1795,13 +1795,13 @@
         <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1778936471174248</v>
+        <v>0.1776197490202196</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1134025292271878</v>
+        <v>0.1134975541628484</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7087038236553874</v>
+        <v>0.7088826968169321</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
-        <v>0.2912961763446126</v>
+        <v>0.2911173031830679</v>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="AA20" t="n">
-        <v>9.564808817230629</v>
+        <v>1.100360164000171</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.564808817230629</v>
+        <v>1.100360164000171</v>
       </c>
     </row>
     <row r="21">
@@ -2278,99 +2278,369 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
+          <t>06NAdG8N</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45523.54166666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>cottbus</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>werder bremen</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>59</v>
+      </c>
+      <c r="F28" t="n">
+        <v>593</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45523.54166666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>offenbach</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>magdeburg</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>59</v>
+      </c>
+      <c r="F29" t="n">
+        <v>593</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45523.54166666666</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>tus koblenz</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>wolfsburg</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>59</v>
+      </c>
+      <c r="F30" t="n">
+        <v>593</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45523.65625</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>braunschweig</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>eintracht frankfurt</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>59</v>
+      </c>
+      <c r="F31" t="n">
+        <v>593</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.03980787590673734</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.07123388984010177</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.8889582342531608</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="n">
+        <v>0.1110417657468392</v>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.4197137519209032</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.4197137519209032</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B32" s="2" t="n">
         <v>45521.64583333334</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>bayer leverkusen</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>stuttgart</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>59</v>
-      </c>
-      <c r="F28" t="n">
+      <c r="E32" t="n">
+        <v>59</v>
+      </c>
+      <c r="F32" t="n">
         <v>594</v>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>super cup</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="J28" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="K28" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.5510584327947249</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.2272798605305432</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0.221661706674732</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0.01379306554446913</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="I32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.5185185185185186</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.2592592592592593</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
         <v>0.7990466275754536</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R32" t="n">
         <v>0.03928553527936484</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S32" t="n">
         <v>0.1616678371451817</v>
       </c>
-      <c r="T28" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0.2479881947807288</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0.2479881947807288</v>
-      </c>
-      <c r="X28" t="n">
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.280528109056935</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.280528109056935</v>
+      </c>
+      <c r="X32" t="n">
         <v>0.7990466275754536</v>
       </c>
-      <c r="Y28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Y32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z32" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
-      <c r="AA28" t="n">
-        <v>34.95233137877268</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>34.95233137877268</v>
+      <c r="AA32" t="n">
+        <v>3.020222668144887</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>3.020222668144887</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/germany/predicciones.xlsx
+++ b/p6_deployment/data/germany/predicciones.xlsx
@@ -679,13 +679,13 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.09632788562397251</v>
+        <v>0.0971796147990323</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1182393982592243</v>
+        <v>0.1193467756926307</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7854327161168032</v>
+        <v>0.7834736095083371</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -696,7 +696,7 @@
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>0.2145672838831968</v>
+        <v>0.2165263904916629</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>0.8110177206963003</v>
+        <v>1.450043520282718</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8110177206963003</v>
+        <v>1.450043520282718</v>
       </c>
     </row>
     <row r="4">
@@ -1269,13 +1269,13 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.06117359204943089</v>
+        <v>0.05890705866981628</v>
       </c>
       <c r="R12" t="n">
-        <v>0.08600848854088683</v>
+        <v>0.0850825161689492</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8528179194096823</v>
+        <v>0.8560104251612345</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
-        <v>0.1471820805903177</v>
+        <v>0.1439895748387655</v>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr">
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>0.5563162909433954</v>
+        <v>0.9642757610705874</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.5563162909433954</v>
+        <v>0.9642757610705874</v>
       </c>
     </row>
     <row r="13">
@@ -1795,13 +1795,13 @@
         <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1776197490202196</v>
+        <v>0.1794567954919975</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1134975541628484</v>
+        <v>0.1125722033075784</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7088826968169321</v>
+        <v>0.7079710012004241</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
-        <v>0.2911173031830679</v>
+        <v>0.2920289987995759</v>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="AA20" t="n">
-        <v>1.100360164000171</v>
+        <v>1.955672731081154</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.100360164000171</v>
+        <v>1.955672731081154</v>
       </c>
     </row>
     <row r="21">
@@ -2513,13 +2513,13 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.03980787590673734</v>
+        <v>0.03866522508709244</v>
       </c>
       <c r="R31" t="n">
-        <v>0.07123388984010177</v>
+        <v>0.0701925108605358</v>
       </c>
       <c r="S31" t="n">
-        <v>0.8889582342531608</v>
+        <v>0.8911422640523718</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="n">
-        <v>0.1110417657468392</v>
+        <v>0.1088577359476282</v>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr">
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="AA31" t="n">
-        <v>0.4197137519209032</v>
+        <v>0.7290033066411972</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.4197137519209032</v>
+        <v>0.7290033066411972</v>
       </c>
     </row>
     <row r="32">
@@ -2581,55 +2581,55 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K32" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L32" t="n">
-        <v>0.5185185185185186</v>
+        <v>0.4926019487549621</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2592592592592593</v>
+        <v>0.2674124864669794</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2399855647780585</v>
       </c>
       <c r="O32" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.06844033159822627</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.7990466275754536</v>
+        <v>0.7830864358157542</v>
       </c>
       <c r="R32" t="n">
-        <v>0.03928553527936484</v>
+        <v>0.04088231273115332</v>
       </c>
       <c r="S32" t="n">
-        <v>0.1616678371451817</v>
+        <v>0.1760312514530925</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0.280528109056935</v>
+        <v>0.2904844870607921</v>
       </c>
       <c r="V32" t="n">
         <v>1</v>
       </c>
       <c r="W32" t="n">
-        <v>0.280528109056935</v>
+        <v>0.2904844870607921</v>
       </c>
       <c r="X32" t="n">
-        <v>0.7990466275754536</v>
+        <v>0.7830864358157542</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="AA32" t="n">
-        <v>3.020222668144887</v>
+        <v>5.24420792078758</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.020222668144887</v>
+        <v>5.24420792078758</v>
       </c>
     </row>
   </sheetData>
